--- a/Assets/ExcelTools/Excels/MonsterCfg.xlsx
+++ b/Assets/ExcelTools/Excels/MonsterCfg.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="14670"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -45,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -72,117 +85,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
+  <si>
+    <t>怪物id</t>
+  </si>
+  <si>
+    <t>怪物名称</t>
+  </si>
+  <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
+    <t>怪物描述</t>
+  </si>
+  <si>
+    <t>技能数组</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>法力值</t>
+  </si>
+  <si>
+    <t>魔法攻击力</t>
+  </si>
+  <si>
+    <t>物理攻击力</t>
+  </si>
+  <si>
+    <t>物理防御力</t>
+  </si>
+  <si>
+    <t>魔法防御力</t>
+  </si>
+  <si>
+    <t>物理暴击率</t>
+  </si>
+  <si>
+    <t>魔法暴击率</t>
+  </si>
+  <si>
+    <t>物理暴击倍率</t>
+  </si>
+  <si>
+    <t>魔法暴击倍率</t>
+  </si>
+  <si>
+    <t>力量</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>智力</t>
+  </si>
+  <si>
+    <t>精神</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>MonsterDes</t>
+  </si>
+  <si>
+    <t>skillidArr</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>mp</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>adDef</t>
+  </si>
+  <si>
+    <t>apDef</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>mct</t>
+  </si>
+  <si>
+    <t>adPctRate</t>
+  </si>
+  <si>
+    <t>apMctRate</t>
+  </si>
+  <si>
+    <t>str</t>
+  </si>
+  <si>
+    <t>sta</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>spi</t>
+  </si>
+  <si>
+    <t>agl</t>
+  </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>Array</t>
-  </si>
-  <si>
-    <t>血量</t>
-  </si>
-  <si>
-    <t>法力值</t>
-  </si>
-  <si>
-    <t>魔法攻击力</t>
-  </si>
-  <si>
-    <t>物理攻击力</t>
-  </si>
-  <si>
-    <t>物理防御力</t>
-  </si>
-  <si>
-    <t>魔法防御力</t>
-  </si>
-  <si>
-    <t>物理暴击率</t>
-  </si>
-  <si>
-    <t>魔法暴击率</t>
-  </si>
-  <si>
-    <t>物理暴击倍率</t>
-  </si>
-  <si>
-    <t>魔法暴击倍率</t>
-  </si>
-  <si>
-    <t>力量</t>
-  </si>
-  <si>
-    <t>体力</t>
-  </si>
-  <si>
-    <t>智力</t>
-  </si>
-  <si>
-    <t>精神</t>
-  </si>
-  <si>
-    <t>敏捷</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>MonsterDes</t>
-  </si>
-  <si>
-    <t>skillidArr</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>mp</t>
-  </si>
-  <si>
-    <t>ap</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t>adDef</t>
-  </si>
-  <si>
-    <t>apDef</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>mct</t>
-  </si>
-  <si>
-    <t>adPctRate</t>
-  </si>
-  <si>
-    <t>apMctRate</t>
-  </si>
-  <si>
-    <t>str</t>
-  </si>
-  <si>
-    <t>sta</t>
-  </si>
-  <si>
-    <t>Int</t>
-  </si>
-  <si>
-    <t>spi</t>
-  </si>
-  <si>
-    <t>agl</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>20001</t>
@@ -269,14 +303,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,22 +319,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,6 +337,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,8 +366,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,14 +397,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
@@ -359,24 +413,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,14 +428,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
@@ -405,28 +435,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -456,181 +501,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,11 +717,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -696,15 +780,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -720,32 +795,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -760,160 +814,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -934,52 +979,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1250,8 +1295,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="12.75" customWidth="1"/>
     <col min="4" max="4" width="29.125" customWidth="1"/>
@@ -1271,192 +1316,196 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3"/>
@@ -1464,278 +1513,336 @@
         <v>47</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="3">
-        <v>980</v>
-      </c>
-      <c r="K5" s="3">
-        <v>980</v>
+        <v>55</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J6" s="3">
-        <v>860</v>
+        <v>980</v>
       </c>
       <c r="K6" s="3">
-        <v>860</v>
+        <v>980</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="J7" s="3">
+        <v>860</v>
+      </c>
+      <c r="K7" s="3">
+        <v>860</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="3">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>42</v>
+      <c r="I9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
